--- a/tables/UnitState.xlsx
+++ b/tables/UnitState.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[초안 10/29] 한 행 = 상태 하나(오브젝트 하나). 같은 UnitID 행들이 그 보스의 상태 배열이 된다. Phase 0부터. 남은 HP 비율이 HPThreshold(최대 HP 대비 만분율) 이하가 되면 그 상태로 넘어가고 되돌아가지 않음. HPThreshold·ExecuteDamage는 만분율. AttackIDs는 | 구분. 공격 목록·대기 등 값은 자리 채움.</t>
+          <t>[초안 10/29 · 구조 예시] 아래 상태(평상·분노·광분·발악, HP 70/40/10%)와 모든 값은 구조를 보여 주는 예시이며 미확정. 현재 기준은 전투 기획서 C09. 한 행 = 상태 하나(오브젝트 하나). 같은 UnitID 행들이 그 보스의 상태 배열이 된다. Phase 0부터. 남은 HP 비율이 HPThreshold(최대 HP 대비 만분율) 이하가 되면 그 상태로 넘어감. AttackIDs는 | 구분.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[초안 10/29] 한 행 = 상태 하나(오브젝트 하나). 같은 UnitID 행들이 그 플레이어의 상태 배열이 된다. 플레이어 상태 = 상태이상(스턴·독·출혈 등). Duration·TickInterval은 ms, TickDamage는 정수, 플래그는 Y/N. 0 = 미정.</t>
+          <t>[초안 10/29 · 구조 예시] 아래 상태이상(스턴·독·출혈) 목록과 값은 구조를 보여 주는 예시이며 미확정. 한 행 = 상태 하나(오브젝트 하나). 같은 UnitID 행들이 그 플레이어의 상태 배열이 된다. Duration·TickInterval은 ms, TickDamage는 정수, 플래그는 Y/N. 0 = 미정.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[초안 10/29] BossState와 같은 형식. 한 행 = 상태 하나, 같은 UnitID 행들이 그 엘리트 몬스터의 상태 배열. 일반 몬스터는 상태 단계 없음(여기에 넣지 않음). 엘리트는 UnitStat Type = Elite. 아직 엘리트 몬스터가 없어 행 없음.</t>
+          <t>[초안 10/29 · 구조 예시, 미확정] BossState와 같은 형식. 한 행 = 상태 하나, 같은 UnitID 행들이 그 엘리트 몬스터의 상태 배열. 일반 몬스터는 상태 단계 없음(여기에 넣지 않음). 엘리트는 UnitStat Type = Elite. 아직 엘리트 몬스터가 없어 행 없음.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>

--- a/tables/UnitState.xlsx
+++ b/tables/UnitState.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.5" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,6 @@
     <col width="9.630000000000001" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12.75" customWidth="1" min="12" max="12"/>
-    <col width="36.63" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,7 +477,6 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -501,7 +499,6 @@
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -524,7 +521,6 @@
       <c r="J3" s="1" t="n"/>
       <c r="K3" s="1" t="n"/>
       <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -547,7 +543,6 @@
       <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="n"/>
       <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -570,7 +565,6 @@
       <c r="J5" s="1" t="n"/>
       <c r="K5" s="1" t="n"/>
       <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -634,11 +628,6 @@
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -689,11 +678,6 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
           <t>State0 평상. ExecuteDamage 1800 = 최대 HP 18%</t>
         </is>
       </c>
@@ -743,11 +727,6 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
           <t>State1 분노: 남은 HP 70% 이하</t>
         </is>
       </c>
@@ -797,11 +776,6 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
           <t>State2 광분: 남은 HP 40% 이하. 문 돌진 추가, 대기 짧아짐</t>
         </is>
       </c>
@@ -850,11 +824,6 @@
         <v>1800</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>State3 발악: 남은 HP 10% 이하</t>
         </is>
@@ -871,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,7 +864,6 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -918,7 +886,6 @@
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -941,7 +908,6 @@
       <c r="J3" s="1" t="n"/>
       <c r="K3" s="1" t="n"/>
       <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -964,7 +930,6 @@
       <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="n"/>
       <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -987,7 +952,6 @@
       <c r="J5" s="1" t="n"/>
       <c r="K5" s="1" t="n"/>
       <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1042,16 +1006,11 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
+      <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1094,16 +1053,11 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
           <t>행동 불가. 시간 미정</t>
         </is>
       </c>
+      <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1146,11 +1100,6 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
           <t>일정 간격 피해. 값 미정</t>
         </is>
       </c>
@@ -1195,11 +1144,6 @@
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>일정 간격 피해, 중첩 가능(안). 값 미정</t>
         </is>
@@ -1216,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,7 +1184,6 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1263,7 +1206,6 @@
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1286,7 +1228,6 @@
       <c r="J3" s="1" t="n"/>
       <c r="K3" s="1" t="n"/>
       <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1309,7 +1250,6 @@
       <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="n"/>
       <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1332,7 +1272,6 @@
       <c r="J5" s="1" t="n"/>
       <c r="K5" s="1" t="n"/>
       <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1396,11 +1335,6 @@
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1420,7 +1354,6 @@
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/UnitState.xlsx
+++ b/tables/UnitState.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>보스 상태(평상·분노·광분·발악)별 공격 목록·대기·체세 회복·해체 피해.</t>
+          <t>JSON,보스 상태(평상·분노·광분·발악)별 공격 목록·대기·체세 회복·해체 피해.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -873,7 +873,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>플레이어가 받는 상태이상의 지속·피해·행동 제한.</t>
+          <t>JSON,플레이어가 받는 상태이상의 지속·피해·행동 제한.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>엘리트 몬스터 상태(평상·분노 등)별 공격 목록·대기·체세 회복.</t>
+          <t>JSON,엘리트 몬스터 상태(평상·분노 등)별 공격 목록·대기·체세 회복.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/UnitState.xlsx
+++ b/tables/UnitState.xlsx
@@ -442,18 +442,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.5" customWidth="1" min="1" max="1"/>
     <col width="5.5" customWidth="1" min="4" max="4"/>
     <col width="10.5" customWidth="1" min="6" max="6"/>
-    <col width="35.5" customWidth="1" min="7" max="7"/>
+    <col width="7.38" customWidth="1" min="7" max="7"/>
     <col width="7.38" customWidth="1" min="8" max="8"/>
     <col width="13.75" customWidth="1" min="9" max="9"/>
     <col width="9.630000000000001" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12.75" customWidth="1" min="12" max="12"/>
+    <col width="12.75" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,7 +465,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[초안 10/29 · 구조 예시] 아래 상태(평상·분노·광분·발악, HP 70/40/10%)와 모든 값은 구조를 보여 주는 예시이며 미확정. 현재 기준은 전투 기획서 C09. 한 행 = 상태 하나(오브젝트 하나). 같은 UnitID 행들이 그 보스의 상태 배열이 된다. Phase 0부터. 남은 HP 비율이 HPThreshold(최대 HP 대비 만분율) 이하가 되면 그 상태로 넘어감. AttackIDs는 | 구분.</t>
+          <t>[초안 10/29 · 구조 예시] 아래 상태(평상·분노·광분·발악, HP 70/40/10%)와 모든 값은 구조를 보여 주는 예시이며 미확정. 현재 기준은 전투 기획서 C09. 한 행 = 상태 하나(오브젝트 하나). 같은 UnitID 행들이 그 보스의 상태 배열이 된다. Phase 0부터. 남은 HP 비율이 HPThreshold(최대 HP 대비 만분율) 이하가 되면 그 상태로 넘어감. IdleMin~SuperArmor는 Monster와 같은 열·같은 순서(몬스터 공통). ExecuteType DAMAGE = 해체 시 ExecuteDamage(최대 HP 대비 만분율)만큼 피해. 공격 패턴은 데이터로 두지 않음(Attack 삭제, 10/29).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -486,7 +487,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>JSON,보스 상태(평상·분노·광분·발악)별 공격 목록·대기·체세 회복·해체 피해.</t>
+          <t>JSON,보스 상태(평상·분노·광분·발악)별 대기·체세 회복·해체 피해.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -599,12 +600,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>AttackIDs</t>
+          <t>IdleMin</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>IdleTime</t>
+          <t>IdleMax</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -624,10 +625,20 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>ExecuteType</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>ExecuteDamage</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -656,10 +667,8 @@
       <c r="F7" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>5013|5014|5015</t>
-        </is>
+      <c r="G7" s="3" t="n">
+        <v>1500</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1500</v>
@@ -673,10 +682,20 @@
       <c r="K7" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>State0 평상. ExecuteDamage 1800 = 최대 HP 18%</t>
         </is>
@@ -705,10 +724,8 @@
       <c r="F8" s="3" t="n">
         <v>7000</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>5013|5014|5015</t>
-        </is>
+      <c r="G8" s="3" t="n">
+        <v>1500</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1500</v>
@@ -722,10 +739,20 @@
       <c r="K8" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>State1 분노: 남은 HP 70% 이하</t>
         </is>
@@ -754,10 +781,8 @@
       <c r="F9" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>5013|5014|5015|5016</t>
-        </is>
+      <c r="G9" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>1000</v>
@@ -771,10 +796,20 @@
       <c r="K9" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>State2 광분: 남은 HP 40% 이하. 문 돌진 추가, 대기 짧아짐</t>
         </is>
@@ -803,10 +838,8 @@
       <c r="F10" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5013|5014|5015|5016</t>
-        </is>
+      <c r="G10" s="3" t="n">
+        <v>1000</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>1000</v>
@@ -820,10 +853,20 @@
       <c r="K10" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>State3 발악: 남은 HP 10% 이하</t>
         </is>
@@ -1160,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,7 +1214,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[초안 10/29 · 구조 예시, 미확정] BossState와 같은 형식. 한 행 = 상태 하나, 같은 UnitID 행들이 그 엘리트 몬스터의 상태 배열. 일반 몬스터는 상태 단계 없음(여기에 넣지 않음). 엘리트는 UnitStat Type = Elite. 아직 엘리트 몬스터가 없어 행 없음.</t>
+          <t>[초안 10/29 · 구조 예시, 미확정] BossState와 같은 형식. 한 행 = 상태 하나, 같은 UnitID 행들이 그 엘리트 몬스터의 상태 배열. 일반 몬스터는 상태 단계 없음(여기에 넣지 않음). 엘리트는 UnitStat Type = Elite. 아직 엘리트 몬스터가 없어 행 없음. IdleMin~SuperArmor는 Monster와 같은 열·같은 순서(몬스터 공통). ExecuteType DAMAGE = 해체 시 ExecuteDamage(최대 HP 대비 만분율)만큼 피해. 공격 패턴은 데이터로 두지 않음(Attack 삭제, 10/29).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -1193,7 +1236,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>JSON,엘리트 몬스터 상태(평상·분노 등)별 공격 목록·대기·체세 회복.</t>
+          <t>JSON,엘리트 몬스터 상태(평상·분노 등)별 대기·체세 회복·해체.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1215,7 +1258,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>엘리트 AI가 읽는다. UnitState.xlsx 안의 시트. 나중에 몬스터 스킬이 생기면 AttackIDs에 스킬 공격을 넣거나 열을 추가.</t>
+          <t>엘리트 AI가 읽는다. UnitState.xlsx 안의 시트. 나중에 몬스터 스킬이 생기면 열을 추가.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1306,12 +1349,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>AttackIDs</t>
+          <t>IdleMin</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>IdleTime</t>
+          <t>IdleMax</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1331,10 +1374,20 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>ExecuteType</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>ExecuteDamage</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>

--- a/tables/UnitState.xlsx
+++ b/tables/UnitState.xlsx
@@ -448,13 +448,12 @@
     <col width="8.5" customWidth="1" min="1" max="1"/>
     <col width="5.5" customWidth="1" min="4" max="4"/>
     <col width="10.5" customWidth="1" min="6" max="6"/>
-    <col width="7.38" customWidth="1" min="7" max="7"/>
+    <col width="35.5" customWidth="1" min="7" max="7"/>
     <col width="7.38" customWidth="1" min="8" max="8"/>
     <col width="13.75" customWidth="1" min="9" max="9"/>
     <col width="9.630000000000001" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12.75" customWidth="1" min="12" max="12"/>
-    <col width="12.75" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,60 +584,60 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>IdleMin</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>IdleMax</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseRegenDelay</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseRegen</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ExposeTime</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ExecuteType</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ExecuteDamage</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>HPThreshold</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>IdleMin</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>IdleMax</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>PoiseRegenDelay</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>PoiseRegen</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>ExposeTime</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>ExecuteType</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>ExecuteDamage</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>SuperArmor</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -657,43 +656,43 @@
         <v>1006</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Idle</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="N7" s="3" t="n">
         <v>10000</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>DAMAGE</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -714,43 +713,43 @@
         <v>1006</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Rage</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="N8" s="3" t="n">
         <v>7000</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>DAMAGE</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -771,43 +770,43 @@
         <v>1006</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Frenzy</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>4000</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>DAMAGE</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -828,43 +827,43 @@
         <v>1006</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Desperate</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>1000</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>DAMAGE</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -1334,57 +1333,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>IdleMin</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>IdleMax</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseRegenDelay</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PoiseRegen</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ExposeTime</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ExecuteType</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ExecuteDamage</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>HPThreshold</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>IdleMin</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>IdleMax</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>PoiseRegenDelay</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>PoiseRegen</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>ExposeTime</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>ExecuteType</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>ExecuteDamage</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>SuperArmor</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1407,6 +1406,8 @@
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
